--- a/capstone-docs/meeting_minutes/Meeting minutes of our group.xlsx
+++ b/capstone-docs/meeting_minutes/Meeting minutes of our group.xlsx
@@ -90,7 +90,7 @@
     <t>MEETING MINUTES OF OUR GROUP — IELTSPath — TUẦN 3</t>
   </si>
   <si>
-    <t>Thời gian tuần: 21/09/2026 – 27/09/2026  ·  Thành viên: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 21/09/2026 – 27/09/2026  ·  Thành viên: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 5 — Thứ Tư, 23/09/2026 · Google Meet · Review user/content service</t>
@@ -120,7 +120,7 @@
     <t>MEETING MINUTES OF OUR GROUP — IELTSPath — TUẦN 4</t>
   </si>
   <si>
-    <t>Thời gian tuần: 28/09/2026 – 04/10/2026  ·  Thành viên: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 28/09/2026 – 04/10/2026  ·  Thành viên: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 7 — Thứ Tư, 30/09/2026 · Google Meet · Review UI và tách service</t>
@@ -144,7 +144,7 @@
     <t>MEETING MINUTES OF OUR GROUP — IELTSPath — TUẦN 5</t>
   </si>
   <si>
-    <t>Thời gian tuần: 05/10/2026 – 11/10/2026  ·  Thành viên: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 05/10/2026 – 11/10/2026  ·  Thành viên: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 9 — Thứ Ba, 06/10/2026 · Google Meet · Hoàn thiện Frontend và tài liệu</t>
@@ -225,7 +225,7 @@
     <t>Thiết kế lesson: một lesson có nhiều block (text, passage, audio, bài tập, essay); skill suy ra từ câu hỏi.</t>
   </si>
   <si>
-    <t>Tính phương án chấm Wrtting: trả band ước tính, tiêu chí, lỗi sửa và bài mẫu. Quyết định giới hạn số lần chấm mỗi ngày để kiểm soát chi phí.</t>
+    <t>Tính phương án chấm Writing: trả band ước tính, tiêu chí, lỗi sửa và bài mẫu. Quyết định giới hạn số lần chấm mỗi ngày để kiểm soát chi phí.</t>
   </si>
   <si>
     <t>demo Frontend đã nối luồng chính với Backend</t>
@@ -291,7 +291,7 @@
     <t xml:space="preserve"> Cập nhật WBS trong Project Tracking: chia iteration 1–3.</t>
   </si>
   <si>
-    <t>Tìm hiểuvà làm  khung Report 4 – TDS: sơ đồ kiến trúc, sơ đồ triển khai, luồng event, thiết kế database từng service.</t>
+    <t>Tìm hiểu và làm khung Report 4 – TDS: sơ đồ kiến trúc, sơ đồ triển khai, luồng event, thiết kế database từng service.</t>
   </si>
 </sst>
 </file>
